--- a/data/students.xlsx
+++ b/data/students.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr defaultThemeVersion="153222"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="30" windowWidth="15000" windowHeight="7740" activeTab="0"/>
+    <workbookView xWindow="240" yWindow="30" windowWidth="15000" windowHeight="7740" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="61" count="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="67" count="67">
   <si>
     <t xml:space="preserve">name </t>
   </si>
@@ -197,6 +197,24 @@
   </si>
   <si>
     <t>USD 1</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Engineer Dimond </t>
+  </si>
+  <si>
+    <t>phone</t>
+  </si>
+  <si>
+    <t>263783702724</t>
+  </si>
+  <si>
+    <t>balance</t>
+  </si>
+  <si>
+    <t>ZWG 15</t>
   </si>
 </sst>
 </file>
@@ -243,7 +261,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -287,6 +305,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -307,7 +328,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr defaultRowHeight="16.25" defaultColWidth="10"/>
   <sheetData>
     <row r="1" spans="8:8">
@@ -483,9 +504,32 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr defaultRowHeight="16.25" defaultColWidth="10"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="8:8">
+      <c r="A1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="8:8">
+      <c r="A2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="C2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="0" scale="285" orientation="landscape"/>
 </worksheet>
@@ -493,7 +537,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr defaultRowHeight="16.25" defaultColWidth="10"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/students.xlsx
+++ b/data/students.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr defaultThemeVersion="153222"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="30" windowWidth="15000" windowHeight="7740" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="30" windowWidth="15000" windowHeight="7740" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="67" count="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="68" count="68">
   <si>
     <t xml:space="preserve">name </t>
   </si>
@@ -215,6 +215,9 @@
   </si>
   <si>
     <t>ZWG 15</t>
+  </si>
+  <si>
+    <t>ZWG 1</t>
   </si>
 </sst>
 </file>
@@ -224,7 +227,7 @@
   <numFmts count="1">
     <numFmt numFmtId="0" formatCode="General"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Arial"/>
       <sz val="11"/>
@@ -233,6 +236,10 @@
       <name val="Arial"/>
       <sz val="11"/>
       <color indexed="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -307,7 +314,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -328,7 +335,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr defaultRowHeight="16.25" defaultColWidth="10"/>
   <sheetData>
     <row r="1" spans="8:8">
@@ -493,7 +500,7 @@
         <v>36</v>
       </c>
       <c r="C15" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -504,7 +511,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="16.25" defaultColWidth="10"/>
   <sheetData>
     <row r="1" spans="8:8">
@@ -537,7 +544,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr defaultRowHeight="16.25" defaultColWidth="10"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
